--- a/SCPGameIDs.xlsx
+++ b/SCPGameIDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/771418921f125165/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FA89670-9B63-470D-BBFD-F64936E9F05B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0FA89670-9B63-470D-BBFD-F64936E9F05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{502D35A8-9036-4E50-ACD1-4D29A10C6558}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="10155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="327">
   <si>
     <t>Id</t>
   </si>
@@ -85,21 +85,6 @@
     <t>D-Class Identification Tag</t>
   </si>
   <si>
-    <t>Janitor IdCard</t>
-  </si>
-  <si>
-    <t>Researcher IdCard</t>
-  </si>
-  <si>
-    <t>Agent IdCard</t>
-  </si>
-  <si>
-    <t>O5 IdCard</t>
-  </si>
-  <si>
-    <t>MTF IdCard</t>
-  </si>
-  <si>
     <t>Keycards</t>
   </si>
   <si>
@@ -445,9 +430,6 @@
     <t>Rusty Key</t>
   </si>
   <si>
-    <t>random</t>
-  </si>
-  <si>
     <t>R4A3</t>
   </si>
   <si>
@@ -916,9 +898,6 @@
     <t>Guest Keycard</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>Temporary: 24h</t>
   </si>
   <si>
@@ -944,6 +923,84 @@
   </si>
   <si>
     <t>SCP Objects</t>
+  </si>
+  <si>
+    <t>0 ~ 1</t>
+  </si>
+  <si>
+    <t>Cracked Keycard</t>
+  </si>
+  <si>
+    <t>Burned Keycard</t>
+  </si>
+  <si>
+    <t>Blood-Stained Keycard</t>
+  </si>
+  <si>
+    <t>Laminated Guest Keycard</t>
+  </si>
+  <si>
+    <t>VIP Guest Keycard</t>
+  </si>
+  <si>
+    <t>1 ~ 2</t>
+  </si>
+  <si>
+    <t>2 ~ 4</t>
+  </si>
+  <si>
+    <t>Works Intermittenly</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>"Grey" Card</t>
+  </si>
+  <si>
+    <t>Old variant. Suspicious</t>
+  </si>
+  <si>
+    <t>Low-quality Conterfeit Keycard</t>
+  </si>
+  <si>
+    <t>High-quality  Conterfeit Keycard</t>
+  </si>
+  <si>
+    <t>Old (random)</t>
+  </si>
+  <si>
+    <t>Ideal Conterfeit Keycard</t>
+  </si>
+  <si>
+    <t>4 ~ 5</t>
+  </si>
+  <si>
+    <t>Blank Keycard</t>
+  </si>
+  <si>
+    <t>blank</t>
+  </si>
+  <si>
+    <t>Preparation for Keycard</t>
+  </si>
+  <si>
+    <t>Brass Cell Key</t>
+  </si>
+  <si>
+    <t>D-Cells</t>
+  </si>
+  <si>
+    <t>Heavy Iron Key</t>
+  </si>
+  <si>
+    <t>Heavy Gates</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>Personnel ID Badge</t>
   </si>
 </sst>
 </file>
@@ -1145,7 +1202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1193,10 +1250,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1555,25 +1609,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="J1" s="18" t="s">
-        <v>193</v>
+        <v>185</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1584,13 +1638,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="G2" s="16">
         <v>0</v>
@@ -1604,7 +1658,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G3" s="16">
         <v>1</v>
@@ -1618,7 +1672,7 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="G4" s="16">
         <v>2</v>
@@ -1632,7 +1686,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="G5" s="16">
         <v>3</v>
@@ -1646,7 +1700,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="G6" s="16">
         <v>4</v>
@@ -1660,7 +1714,7 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G7" s="16">
         <v>5</v>
@@ -1674,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1682,74 +1736,139 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E9" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6"/>
+      <c r="B11" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="6"/>
+      <c r="B12" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E12" t="s">
+        <v>309</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6"/>
+      <c r="B13" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E13" t="s">
+        <v>309</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="6"/>
+      <c r="B14" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E14" t="s">
+        <v>309</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E15" t="s">
+        <v>312</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="6"/>
+      <c r="B19" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E19" t="s">
+        <v>320</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="5">
@@ -1825,7 +1944,7 @@
         <v>9</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G31" s="16">
         <v>0</v>
@@ -1857,12 +1976,7 @@
       <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>141</v>
-      </c>
+      <c r="B34" s="6"/>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="5">
@@ -1874,19 +1988,37 @@
       <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="6"/>
+      <c r="B36" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" t="s">
+        <v>309</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="6"/>
+      <c r="B38" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="5">
@@ -1968,7 +2100,7 @@
         <v>18</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -2035,7 +2167,7 @@
         <v>20</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -2043,40 +2175,32 @@
         <v>61</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B63" s="6"/>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="B64" s="6"/>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="B65" s="6"/>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="B66" s="6"/>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="5">
@@ -2200,7 +2324,7 @@
         <v>12</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -2303,10 +2427,10 @@
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2314,7 +2438,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2322,7 +2446,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2330,7 +2454,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2338,7 +2462,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2346,7 +2470,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2354,7 +2478,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2362,7 +2486,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2370,7 +2494,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2378,7 +2502,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2386,7 +2510,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2628,10 +2752,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2639,7 +2763,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2647,7 +2771,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2655,7 +2779,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2663,7 +2787,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2671,7 +2795,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2823,10 +2947,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -2834,7 +2958,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -2842,7 +2966,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -2850,7 +2974,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -2858,7 +2982,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -2866,7 +2990,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -2874,7 +2998,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -2882,7 +3006,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -2890,7 +3014,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -2964,10 +3088,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -2975,7 +3099,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -2983,7 +3107,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -2991,7 +3115,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -3035,13 +3159,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E211" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3103,13 +3227,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -3117,7 +3241,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -3125,7 +3249,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -3139,7 +3263,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3147,7 +3271,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3155,7 +3279,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3163,7 +3287,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3243,10 +3367,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -3254,7 +3378,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -3370,10 +3494,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -3381,7 +3505,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -3389,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -3397,7 +3521,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -3501,13 +3625,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E281" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -3515,7 +3639,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -3631,13 +3755,13 @@
         <v>300</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -3645,7 +3769,7 @@
         <v>301</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -3881,25 +4005,25 @@
         <v>340</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D341" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E341" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F341" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G341" s="16" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H341" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -3907,19 +4031,19 @@
         <v>341</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E342" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F342" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G342" s="16">
         <v>2</v>
       </c>
       <c r="H342" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -3928,16 +4052,16 @@
       </c>
       <c r="B343" s="6"/>
       <c r="E343" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F343" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G343" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H343" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -3945,19 +4069,19 @@
         <v>343</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E344" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F344" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G344" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H344" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -3965,19 +4089,19 @@
         <v>344</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E345" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F345" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G345" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H345" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -3985,19 +4109,19 @@
         <v>345</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E346" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F346" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G346" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H346" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -4005,19 +4129,19 @@
         <v>346</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E347" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F347" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G347" s="16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H347" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="348" spans="1:9">
@@ -4025,19 +4149,19 @@
         <v>347</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E348" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F348" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G348" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H348" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -4045,19 +4169,19 @@
         <v>348</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E349" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F349" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G349" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H349" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -4065,19 +4189,19 @@
         <v>349</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E350" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F350" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G350" s="16" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H350" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -4085,19 +4209,19 @@
         <v>350</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E351" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F351" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G351" s="16" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H351" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -4106,19 +4230,19 @@
       </c>
       <c r="B352" s="6"/>
       <c r="E352" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F352" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G352" s="16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H352" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I352" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -4126,22 +4250,22 @@
         <v>352</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E353" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="F353" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G353" s="16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H353" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="I353" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="354" spans="1:9">
@@ -4192,10 +4316,10 @@
       </c>
       <c r="B361" s="6"/>
       <c r="C361" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E361" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="362" spans="1:9">
@@ -4204,7 +4328,7 @@
       </c>
       <c r="B362" s="6"/>
       <c r="E362" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -4213,7 +4337,7 @@
       </c>
       <c r="B363" s="6"/>
       <c r="E363" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="364" spans="1:9">
@@ -4222,7 +4346,7 @@
       </c>
       <c r="B364" s="6"/>
       <c r="E364" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -4231,7 +4355,7 @@
       </c>
       <c r="B365" s="6"/>
       <c r="E365" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="366" spans="1:9">
@@ -4240,7 +4364,7 @@
       </c>
       <c r="B366" s="6"/>
       <c r="E366" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="367" spans="1:9">
@@ -4249,7 +4373,7 @@
       </c>
       <c r="B367" s="6"/>
       <c r="E367" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="368" spans="1:9">
@@ -4258,7 +4382,7 @@
       </c>
       <c r="B368" s="6"/>
       <c r="E368" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -4279,13 +4403,13 @@
       </c>
       <c r="B371" s="6"/>
       <c r="C371" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E371" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F371" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -4294,10 +4418,10 @@
       </c>
       <c r="B372" s="6"/>
       <c r="E372" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F372" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -4305,10 +4429,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E373" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -4358,22 +4482,22 @@
         <v>380</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E381" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F381" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G381" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H381" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -4381,19 +4505,19 @@
         <v>381</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E382" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F382" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G382" s="16" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H382" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -4401,19 +4525,19 @@
         <v>382</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E383" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="F383" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G383" s="16" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H383" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -4421,19 +4545,19 @@
         <v>383</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E384" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F384" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G384" s="16" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H384" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -4441,19 +4565,19 @@
         <v>384</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E385" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F385" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G385" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H385" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -4461,19 +4585,19 @@
         <v>385</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E386" t="s">
+        <v>163</v>
+      </c>
+      <c r="F386" t="s">
         <v>169</v>
       </c>
-      <c r="F386" t="s">
-        <v>175</v>
-      </c>
       <c r="G386" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H386" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -4481,19 +4605,19 @@
         <v>386</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E387" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F387" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G387" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H387" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -4501,19 +4625,19 @@
         <v>387</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E388" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F388" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G388" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H388" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -4521,19 +4645,19 @@
         <v>388</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E389" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F389" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G389" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H389" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -4541,19 +4665,19 @@
         <v>389</v>
       </c>
       <c r="B390" s="6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E390" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F390" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G390" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H390" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -4561,25 +4685,25 @@
         <v>390</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E391" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F391" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G391" s="16" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H391" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="I391" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="J391" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -4588,16 +4712,16 @@
       </c>
       <c r="B392" s="6"/>
       <c r="E392" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F392" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G392" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H392" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -4605,19 +4729,19 @@
         <v>392</v>
       </c>
       <c r="B393" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E393" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F393" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G393" s="16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H393" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -4625,19 +4749,19 @@
         <v>393</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E394" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F394" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G394" s="16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H394" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -4645,19 +4769,19 @@
         <v>394</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E395" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F395" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G395" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H395" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -4665,19 +4789,19 @@
         <v>395</v>
       </c>
       <c r="B396" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E396" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F396" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G396" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H396" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -4685,19 +4809,19 @@
         <v>396</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="E397" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F397" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G397" s="16" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H397" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -4705,19 +4829,19 @@
         <v>397</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E398" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F398" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G398" s="16" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H398" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -4725,19 +4849,19 @@
         <v>398</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="E399" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F399" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G399" s="16" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H399" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -4745,19 +4869,19 @@
         <v>399</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E400" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F400" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G400" s="16" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H400" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="401" spans="1:9">
@@ -4765,22 +4889,22 @@
         <v>400</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E401" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F401" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G401" s="16" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H401" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I401" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="402" spans="1:9">
@@ -4788,22 +4912,22 @@
         <v>401</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E402" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="F402" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G402" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H402" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I402" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="403" spans="1:9">
@@ -4859,22 +4983,22 @@
         <v>410</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E411" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F411" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G411" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H411" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="412" spans="1:9">
@@ -4882,19 +5006,19 @@
         <v>411</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E412" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F412" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G412" s="16" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H412" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="413" spans="1:9">
@@ -4902,19 +5026,19 @@
         <v>412</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E413" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="F413" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G413" s="16" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H413" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="414" spans="1:9">
@@ -4922,19 +5046,19 @@
         <v>413</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E414" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F414" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G414" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H414" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="415" spans="1:9">
@@ -4942,19 +5066,19 @@
         <v>414</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="E415" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="F415" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G415" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H415" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="416" spans="1:9">
@@ -4962,19 +5086,19 @@
         <v>415</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E416" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F416" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="G416" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H416" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="417" spans="1:9">
@@ -4983,16 +5107,16 @@
       </c>
       <c r="B417" s="6"/>
       <c r="E417" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="F417" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="G417" s="16" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H417" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="418" spans="1:9">
@@ -5001,16 +5125,16 @@
       </c>
       <c r="B418" s="6"/>
       <c r="E418" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F418" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G418" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H418" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="419" spans="1:9">
@@ -5018,19 +5142,19 @@
         <v>418</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E419" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F419" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="G419" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H419" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="420" spans="1:9">
@@ -5038,19 +5162,19 @@
         <v>419</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E420" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="F420" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G420" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H420" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="421" spans="1:9">
@@ -5058,19 +5182,19 @@
         <v>420</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E421" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="F421" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G421" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H421" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="422" spans="1:9">
@@ -5078,19 +5202,19 @@
         <v>421</v>
       </c>
       <c r="B422" s="6" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E422" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F422" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G422" s="16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H422" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="423" spans="1:9">
@@ -5098,19 +5222,19 @@
         <v>422</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E423" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="F423" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G423" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H423" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="424" spans="1:9">
@@ -5118,19 +5242,19 @@
         <v>423</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E424" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F424" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G424" s="16" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="H424" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="425" spans="1:9">
@@ -5138,22 +5262,22 @@
         <v>424</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E425" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F425" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G425" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H425" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I425" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="426" spans="1:9">
@@ -5161,22 +5285,22 @@
         <v>425</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="E426" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="F426" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G426" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H426" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I426" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="427" spans="1:9">
@@ -5184,22 +5308,22 @@
         <v>426</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E427" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="F427" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="G427" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H427" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I427" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="428" spans="1:9">
@@ -5226,7 +5350,7 @@
       </c>
       <c r="B431" s="6"/>
       <c r="C431" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="432" spans="1:9">
@@ -5348,19 +5472,19 @@
         <v>450</v>
       </c>
       <c r="B451" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="E451" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G451" s="16" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H451" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="452" spans="1:9">
@@ -5368,16 +5492,16 @@
         <v>451</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E452" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G452" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H452" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="453" spans="1:9">
@@ -5385,16 +5509,16 @@
         <v>452</v>
       </c>
       <c r="B453" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E453" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="G453" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H453" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="454" spans="1:9">
@@ -5402,16 +5526,16 @@
         <v>453</v>
       </c>
       <c r="B454" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="E454" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="G454" s="16" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="H454" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="455" spans="1:9">
@@ -5419,16 +5543,16 @@
         <v>454</v>
       </c>
       <c r="B455" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E455" t="s">
+        <v>266</v>
+      </c>
+      <c r="G455" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="E455" t="s">
-        <v>272</v>
-      </c>
-      <c r="G455" s="16" t="s">
-        <v>277</v>
-      </c>
       <c r="H455" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="456" spans="1:9">
@@ -5436,16 +5560,16 @@
         <v>455</v>
       </c>
       <c r="B456" s="6" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E456" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="G456" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H456" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="457" spans="1:9">
@@ -5453,13 +5577,13 @@
         <v>456</v>
       </c>
       <c r="B457" s="6" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E457" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G457" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="458" spans="1:9">
@@ -5467,16 +5591,16 @@
         <v>457</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E458" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G458" s="16" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H458" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="459" spans="1:9">
@@ -5484,16 +5608,16 @@
         <v>458</v>
       </c>
       <c r="B459" s="6" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="E459" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="G459" s="16" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H459" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="460" spans="1:9">
@@ -5502,7 +5626,7 @@
       </c>
       <c r="B460" s="6"/>
       <c r="E460" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="461" spans="1:9">
@@ -5511,7 +5635,7 @@
       </c>
       <c r="B461" s="6"/>
       <c r="E461" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="462" spans="1:9">
@@ -5520,7 +5644,7 @@
       </c>
       <c r="B462" s="6"/>
       <c r="E462" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="463" spans="1:9">
@@ -5529,7 +5653,7 @@
       </c>
       <c r="B463" s="6"/>
       <c r="I463" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="464" spans="1:9">
@@ -5538,7 +5662,7 @@
       </c>
       <c r="B464" s="6"/>
       <c r="I464" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="465" spans="1:9">
@@ -5547,7 +5671,7 @@
       </c>
       <c r="B465" s="6"/>
       <c r="I465" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="466" spans="1:9">
@@ -5556,7 +5680,7 @@
       </c>
       <c r="B466" s="6"/>
       <c r="I466" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="467" spans="1:9">
@@ -5565,7 +5689,7 @@
       </c>
       <c r="B467" s="6"/>
       <c r="I467" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="468" spans="1:9">
@@ -5574,7 +5698,7 @@
       </c>
       <c r="B468" s="6"/>
       <c r="I468" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="469" spans="1:9">
@@ -5655,7 +5779,7 @@
       </c>
       <c r="B481" s="6"/>
       <c r="C481" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -5778,10 +5902,10 @@
       </c>
       <c r="B501" s="6"/>
       <c r="C501" s="3" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D501" s="4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -5844,7 +5968,7 @@
       </c>
       <c r="B511" s="6"/>
       <c r="C511" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -5907,7 +6031,7 @@
       </c>
       <c r="B521" s="6"/>
       <c r="C521" s="3" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -5970,7 +6094,7 @@
       </c>
       <c r="B531" s="6"/>
       <c r="C531" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -6033,7 +6157,7 @@
       </c>
       <c r="B541" s="6"/>
       <c r="C541" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -8792,7 +8916,7 @@
     </row>
     <row r="1001" spans="1:4">
       <c r="D1001" s="4" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/SCPGameIDs.xlsx
+++ b/SCPGameIDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20394"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/771418921f125165/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s0195834\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0FA89670-9B63-470D-BBFD-F64936E9F05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{502D35A8-9036-4E50-ACD1-4D29A10C6558}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD4FCA6-B3F3-4C59-87CC-E84B97FB3476}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="409">
   <si>
     <t>Id</t>
   </si>
@@ -58,21 +58,12 @@
     <t>Old Maintenance Key</t>
   </si>
   <si>
-    <t>Hacking Tool</t>
-  </si>
-  <si>
-    <t>Hacked Access Tool</t>
-  </si>
-  <si>
     <t>Chaos Insurgency Cipher</t>
   </si>
   <si>
     <t>Decoder</t>
   </si>
   <si>
-    <t>Counterfeit O5 Idcard</t>
-  </si>
-  <si>
     <t>Lockpick pack</t>
   </si>
   <si>
@@ -271,9 +262,6 @@
     <t>(Not goggles)</t>
   </si>
   <si>
-    <t>(Not SCP-500)</t>
-  </si>
-  <si>
     <t>Casual Flashlight</t>
   </si>
   <si>
@@ -1001,6 +989,264 @@
   </si>
   <si>
     <t>Personnel ID Badge</t>
+  </si>
+  <si>
+    <t>Универсальные ключ-карты, работают по уровню доступа</t>
+  </si>
+  <si>
+    <t>Физические ключи, работают как по уровню доступа, так и по определённым зам. скважинам</t>
+  </si>
+  <si>
+    <t>Части тел или искуственные части биометрии</t>
+  </si>
+  <si>
+    <t>Карточки доступа различного содержания</t>
+  </si>
+  <si>
+    <t>Приборы для взлома и обмана устройств комплекса</t>
+  </si>
+  <si>
+    <t>Rarity / Specify</t>
+  </si>
+  <si>
+    <t>Общие пометки:</t>
+  </si>
+  <si>
+    <t>Rarity (редкость) определяет частоту встречи определённого предмета/сущности среди себе подобных в одинаковой обстановке. Например, карта 5 уровня - обычный предмет, т.к. встречается всегда у представителей соответствующего уровня доступа</t>
+  </si>
+  <si>
+    <t>Master Key</t>
+  </si>
+  <si>
+    <t>Skeleton Key</t>
+  </si>
+  <si>
+    <t>~3</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Security Key</t>
+  </si>
+  <si>
+    <t>Security room</t>
+  </si>
+  <si>
+    <t>Safe Key</t>
+  </si>
+  <si>
+    <t>Key from safe</t>
+  </si>
+  <si>
+    <t>Old Black Key</t>
+  </si>
+  <si>
+    <t>Backdoor</t>
+  </si>
+  <si>
+    <t>Startup Key (standart)</t>
+  </si>
+  <si>
+    <t>Engines start</t>
+  </si>
+  <si>
+    <t>Startup Key (Red)</t>
+  </si>
+  <si>
+    <t>Nuclear start</t>
+  </si>
+  <si>
+    <t>Brain in a Jar</t>
+  </si>
+  <si>
+    <t>Daily Pass Card</t>
+  </si>
+  <si>
+    <t>Foundation pass</t>
+  </si>
+  <si>
+    <t>Eq. personnel lvl</t>
+  </si>
+  <si>
+    <t>Business Card</t>
+  </si>
+  <si>
+    <t>Brut-Force Laptop</t>
+  </si>
+  <si>
+    <t>Counterfeit Omnicard</t>
+  </si>
+  <si>
+    <t>EMP Device</t>
+  </si>
+  <si>
+    <t>Trojan Flash Drive</t>
+  </si>
+  <si>
+    <t>Experimental Neuro-Interface Module</t>
+  </si>
+  <si>
+    <t>Two-hands rule</t>
+  </si>
+  <si>
+    <t>Dangerous and unstable</t>
+  </si>
+  <si>
+    <t>Don't revive corpses, only heal</t>
+  </si>
+  <si>
+    <t>Not SCP-500</t>
+  </si>
+  <si>
+    <t>"Revive" Syringe</t>
+  </si>
+  <si>
+    <t>Crowbar</t>
+  </si>
+  <si>
+    <t>Также сюда подходят некоторые инструменты, по типу монтировки или гаечного ключа</t>
+  </si>
+  <si>
+    <t>Pipe</t>
+  </si>
+  <si>
+    <t>Table Leg</t>
+  </si>
+  <si>
+    <t>Rubber Baton</t>
+  </si>
+  <si>
+    <t>Electric Baton</t>
+  </si>
+  <si>
+    <t>Bat</t>
+  </si>
+  <si>
+    <t>Aluminum Bat</t>
+  </si>
+  <si>
+    <t>Steel Bat</t>
+  </si>
+  <si>
+    <t>M9-Bayonet</t>
+  </si>
+  <si>
+    <t>Combat Knife</t>
+  </si>
+  <si>
+    <t>Cleaver</t>
+  </si>
+  <si>
+    <t>Kitchen Knife</t>
+  </si>
+  <si>
+    <t>Machete</t>
+  </si>
+  <si>
+    <t>Two-Handled Sword</t>
+  </si>
+  <si>
+    <t>Katana</t>
+  </si>
+  <si>
+    <t>"Zweihander"</t>
+  </si>
+  <si>
+    <t>DP-12</t>
+  </si>
+  <si>
+    <t>Mag-7</t>
+  </si>
+  <si>
+    <t>Chiappa Triple-Crown</t>
+  </si>
+  <si>
+    <t>SPAS-12</t>
+  </si>
+  <si>
+    <t>USAS-12</t>
+  </si>
+  <si>
+    <t>Winchester 1887</t>
+  </si>
+  <si>
+    <t>Saiga 12ga</t>
+  </si>
+  <si>
+    <t>Makeshift Grenade</t>
+  </si>
+  <si>
+    <t>M67</t>
+  </si>
+  <si>
+    <t>F-1</t>
+  </si>
+  <si>
+    <t>РГД-5</t>
+  </si>
+  <si>
+    <t>РГД-7</t>
+  </si>
+  <si>
+    <t>Molotov Cocktail</t>
+  </si>
+  <si>
+    <t>Incendiary Grenade</t>
+  </si>
+  <si>
+    <t>Flashbang Grenade</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>D, CI</t>
+  </si>
+  <si>
+    <t>РГО / РГН</t>
+  </si>
+  <si>
+    <t>EMP Grenade</t>
+  </si>
+  <si>
+    <t>Thermite Grenade</t>
+  </si>
+  <si>
+    <t>C4 Pack</t>
+  </si>
+  <si>
+    <t>Breaching Charge</t>
+  </si>
+  <si>
+    <t>Decoy grenade</t>
+  </si>
+  <si>
+    <t>Casual Clothes</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>Scientific Data</t>
+  </si>
+  <si>
+    <t>Personnel Files</t>
+  </si>
+  <si>
+    <t>/* Categories are Size-Expandable */</t>
+  </si>
+  <si>
+    <t>Logs</t>
+  </si>
+  <si>
+    <t>Literature</t>
+  </si>
+  <si>
+    <t>TODO Expand all tools' categories</t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1252,6 +1498,21 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1587,21 +1848,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6835E4CD-DDA5-B743-A043-EC8D32F5BD2C}">
-  <dimension ref="A1:J1001"/>
+  <dimension ref="A1:L1001"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32.875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="3" customWidth="1"/>
     <col min="4" max="4" width="16" style="4" customWidth="1"/>
-    <col min="5" max="5" width="24.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" style="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" thickBot="1">
+    <row r="1" spans="1:12" thickBot="1">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1609,28 +1871,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>133</v>
-      </c>
       <c r="G1" s="15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>181</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -1638,19 +1906,25 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G2" s="16">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="J2" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1658,13 +1932,15 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G3" s="16">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="J3" s="21"/>
+      <c r="L3" s="18"/>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1672,13 +1948,14 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G4" s="16">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="L4" s="18"/>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1686,13 +1963,14 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G5" s="16">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="L5" s="18"/>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1700,13 +1978,14 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G6" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="L6" s="18"/>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1714,13 +1993,14 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G7" s="16">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="L7" s="18"/>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1728,215 +2008,215 @@
         <v>8</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="E12" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="E13" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E14" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="E15" t="s">
-        <v>312</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E19" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="6"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:10">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="6"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:10">
       <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="6"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:10">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="6"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:10">
       <c r="A24" s="5">
         <v>23</v>
       </c>
       <c r="B24" s="6"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:10">
       <c r="A25" s="5">
         <v>24</v>
       </c>
       <c r="B25" s="6"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:10">
       <c r="A26" s="5">
         <v>25</v>
       </c>
       <c r="B26" s="6"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:10">
       <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="6"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:10">
       <c r="A28" s="5">
         <v>27</v>
       </c>
       <c r="B28" s="6"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:10">
       <c r="A29" s="5">
         <v>28</v>
       </c>
       <c r="B29" s="6"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:10">
       <c r="A30" s="5">
         <v>29</v>
       </c>
       <c r="B30" s="6"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:10" ht="15" customHeight="1">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -1944,13 +2224,16 @@
         <v>9</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G31" s="16">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="J31" s="22" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -1960,8 +2243,9 @@
       <c r="G32" s="16">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="J32" s="22"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -1971,224 +2255,284 @@
       <c r="G33" s="16">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="J33" s="22"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="6"/>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="B34" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="J34" s="22"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="6"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="B35" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="5">
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E36" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="5">
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="5">
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="6"/>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="B39" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="6"/>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="B40" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="6"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="B41" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="6"/>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="B42" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="6"/>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="B43" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="5">
         <v>43</v>
       </c>
       <c r="B44" s="6"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:10">
       <c r="A45" s="5">
         <v>44</v>
       </c>
       <c r="B45" s="6"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:10">
       <c r="A46" s="5">
         <v>45</v>
       </c>
       <c r="B46" s="6"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:10">
       <c r="A47" s="5">
         <v>46</v>
       </c>
       <c r="B47" s="6"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:10">
       <c r="A48" s="5">
         <v>47</v>
       </c>
       <c r="B48" s="6"/>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:10">
       <c r="A49" s="5">
         <v>48</v>
       </c>
       <c r="B49" s="6"/>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" spans="1:10">
       <c r="A50" s="5">
         <v>49</v>
       </c>
       <c r="B50" s="6"/>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:10">
       <c r="A51" s="5">
         <v>50</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="J51" s="21" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" s="5">
         <v>51</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="J52" s="21"/>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="6"/>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="B53" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="5">
         <v>53</v>
       </c>
       <c r="B54" s="6"/>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:10">
       <c r="A55" s="5">
         <v>54</v>
       </c>
       <c r="B55" s="6"/>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:10">
       <c r="A56" s="5">
         <v>55</v>
       </c>
       <c r="B56" s="6"/>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:10">
       <c r="A57" s="5">
         <v>56</v>
       </c>
       <c r="B57" s="6"/>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" spans="1:10">
       <c r="A58" s="5">
         <v>57</v>
       </c>
       <c r="B58" s="6"/>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:10">
       <c r="A59" s="5">
         <v>58</v>
       </c>
       <c r="B59" s="6"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:10">
       <c r="A60" s="5">
         <v>59</v>
       </c>
       <c r="B60" s="6"/>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:10">
       <c r="A61" s="5">
         <v>60</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>295</v>
+      </c>
+      <c r="J61" s="21" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="5">
         <v>61</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>322</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="J62" s="21"/>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="6"/>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="B63" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="6"/>
+      <c r="B64" s="6" t="s">
+        <v>349</v>
+      </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="5">
@@ -2286,234 +2630,245 @@
       </c>
       <c r="B80" s="6"/>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:10">
       <c r="A81" s="5">
         <v>80</v>
       </c>
       <c r="B81" s="6"/>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:10">
       <c r="A82" s="5">
         <v>81</v>
       </c>
       <c r="B82" s="6"/>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:10">
       <c r="A83" s="5">
         <v>82</v>
       </c>
       <c r="B83" s="6"/>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:10">
       <c r="A84" s="5">
         <v>83</v>
       </c>
       <c r="B84" s="6"/>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:10">
       <c r="A85" s="5">
         <v>84</v>
       </c>
       <c r="B85" s="6"/>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:10">
       <c r="A86" s="5">
         <v>85</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="J86" s="21" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="5">
         <v>86</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="J87" s="21"/>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="5">
         <v>87</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" s="5">
         <v>88</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="5">
         <v>89</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="5">
         <v>90</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="6"/>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="B92" s="6" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" s="5">
         <v>92</v>
       </c>
       <c r="B93" s="6"/>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:10">
       <c r="A94" s="5">
         <v>93</v>
       </c>
       <c r="B94" s="6"/>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:10">
       <c r="A95" s="5">
         <v>94</v>
       </c>
       <c r="B95" s="6"/>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:10">
       <c r="A96" s="5">
         <v>95</v>
       </c>
       <c r="B96" s="6"/>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:5">
       <c r="A97" s="5">
         <v>96</v>
       </c>
       <c r="B97" s="6"/>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:5">
       <c r="A98" s="5">
         <v>97</v>
       </c>
       <c r="B98" s="6"/>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:5">
       <c r="A99" s="5">
         <v>98</v>
       </c>
       <c r="B99" s="6"/>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:5">
       <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="6"/>
-    </row>
-    <row r="101" spans="1:4">
+      <c r="B100" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E100" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" s="5">
         <v>100</v>
       </c>
       <c r="B101" s="6"/>
       <c r="C101" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" s="5">
         <v>101</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" s="5">
         <v>102</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" s="5">
         <v>103</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" s="5">
         <v>104</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" s="5">
         <v>105</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" s="5">
         <v>106</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" s="5">
         <v>107</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" s="5">
         <v>108</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" s="5">
         <v>109</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" s="5">
         <v>110</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -2752,10 +3107,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="152" spans="1:3">
@@ -2763,7 +3118,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="153" spans="1:3">
@@ -2771,7 +3126,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="154" spans="1:3">
@@ -2779,7 +3134,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="155" spans="1:3">
@@ -2787,7 +3142,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="156" spans="1:3">
@@ -2795,7 +3150,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="157" spans="1:3">
@@ -2947,10 +3302,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="182" spans="1:3">
@@ -2958,7 +3313,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="183" spans="1:3">
@@ -2966,7 +3321,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="184" spans="1:3">
@@ -2974,7 +3329,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="185" spans="1:3">
@@ -2982,7 +3337,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="186" spans="1:3">
@@ -2990,7 +3345,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -2998,7 +3353,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="188" spans="1:3">
@@ -3006,7 +3361,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -3014,7 +3369,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -3088,10 +3443,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -3099,7 +3454,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -3107,7 +3462,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -3115,7 +3470,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -3142,117 +3497,125 @@
       </c>
       <c r="B208" s="6"/>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:10">
       <c r="A209" s="5">
         <v>208</v>
       </c>
       <c r="B209" s="6"/>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:10">
       <c r="A210" s="5">
         <v>209</v>
       </c>
       <c r="B210" s="6"/>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:10">
       <c r="A211" s="5">
         <v>210</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E211" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
       <c r="A212" s="5">
         <v>211</v>
       </c>
-      <c r="B212" s="6"/>
-    </row>
-    <row r="213" spans="1:5">
+      <c r="B212" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E212" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
       <c r="A213" s="5">
         <v>212</v>
       </c>
       <c r="B213" s="6"/>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:10">
       <c r="A214" s="5">
         <v>213</v>
       </c>
       <c r="B214" s="6"/>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:10">
       <c r="A215" s="5">
         <v>214</v>
       </c>
       <c r="B215" s="6"/>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:10">
       <c r="A216" s="5">
         <v>215</v>
       </c>
       <c r="B216" s="6"/>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:10">
       <c r="A217" s="5">
         <v>216</v>
       </c>
       <c r="B217" s="6"/>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:10">
       <c r="A218" s="5">
         <v>217</v>
       </c>
       <c r="B218" s="6"/>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:10">
       <c r="A219" s="5">
         <v>218</v>
       </c>
       <c r="B219" s="6"/>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:10">
       <c r="A220" s="5">
         <v>219</v>
       </c>
       <c r="B220" s="6"/>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:10">
       <c r="A221" s="5">
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5">
+        <v>58</v>
+      </c>
+      <c r="J221" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
       <c r="A222" s="5">
         <v>221</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
       <c r="A223" s="5">
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
       <c r="A224" s="5">
         <v>223</v>
       </c>
@@ -3263,7 +3626,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3271,7 +3634,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3279,7 +3642,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3287,14 +3650,16 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" s="5">
         <v>228</v>
       </c>
-      <c r="B229" s="6"/>
+      <c r="B229" s="6" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" s="5">
@@ -3367,10 +3732,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -3378,7 +3743,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -3494,10 +3859,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -3505,7 +3870,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -3513,7 +3878,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -3521,7 +3886,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -3625,13 +3990,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E281" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -3639,7 +4004,7 @@
         <v>281</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -3678,203 +4043,240 @@
       </c>
       <c r="B288" s="6"/>
     </row>
-    <row r="289" spans="1:4">
+    <row r="289" spans="1:10">
       <c r="A289" s="5">
         <v>288</v>
       </c>
       <c r="B289" s="6"/>
     </row>
-    <row r="290" spans="1:4">
+    <row r="290" spans="1:10">
       <c r="A290" s="5">
         <v>289</v>
       </c>
       <c r="B290" s="6"/>
     </row>
-    <row r="291" spans="1:4">
+    <row r="291" spans="1:10">
       <c r="A291" s="5">
         <v>290</v>
       </c>
       <c r="B291" s="6"/>
     </row>
-    <row r="292" spans="1:4">
+    <row r="292" spans="1:10">
       <c r="A292" s="5">
         <v>291</v>
       </c>
       <c r="B292" s="6"/>
     </row>
-    <row r="293" spans="1:4">
+    <row r="293" spans="1:10">
       <c r="A293" s="5">
         <v>292</v>
       </c>
       <c r="B293" s="6"/>
     </row>
-    <row r="294" spans="1:4">
+    <row r="294" spans="1:10">
       <c r="A294" s="5">
         <v>293</v>
       </c>
       <c r="B294" s="6"/>
     </row>
-    <row r="295" spans="1:4">
+    <row r="295" spans="1:10">
       <c r="A295" s="5">
         <v>294</v>
       </c>
       <c r="B295" s="6"/>
     </row>
-    <row r="296" spans="1:4">
+    <row r="296" spans="1:10">
       <c r="A296" s="5">
         <v>295</v>
       </c>
       <c r="B296" s="6"/>
     </row>
-    <row r="297" spans="1:4">
+    <row r="297" spans="1:10">
       <c r="A297" s="5">
         <v>296</v>
       </c>
       <c r="B297" s="6"/>
     </row>
-    <row r="298" spans="1:4">
+    <row r="298" spans="1:10">
       <c r="A298" s="5">
         <v>297</v>
       </c>
       <c r="B298" s="6"/>
     </row>
-    <row r="299" spans="1:4">
+    <row r="299" spans="1:10">
       <c r="A299" s="5">
         <v>298</v>
       </c>
       <c r="B299" s="6"/>
     </row>
-    <row r="300" spans="1:4">
+    <row r="300" spans="1:10">
       <c r="A300" s="5">
         <v>299</v>
       </c>
       <c r="B300" s="6"/>
     </row>
-    <row r="301" spans="1:4">
+    <row r="301" spans="1:10">
       <c r="A301" s="5">
         <v>300</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="302" spans="1:10" ht="15" customHeight="1">
       <c r="A302" s="5">
         <v>301</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4">
+        <v>85</v>
+      </c>
+      <c r="J302" s="21" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="303" spans="1:10">
       <c r="A303" s="5">
         <v>302</v>
       </c>
-      <c r="B303" s="6"/>
-    </row>
-    <row r="304" spans="1:4">
+      <c r="B303" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="J303" s="21"/>
+    </row>
+    <row r="304" spans="1:10">
       <c r="A304" s="5">
         <v>303</v>
       </c>
-      <c r="B304" s="6"/>
-    </row>
-    <row r="305" spans="1:2">
+      <c r="B304" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="J304" s="21"/>
+    </row>
+    <row r="305" spans="1:10">
       <c r="A305" s="5">
         <v>304</v>
       </c>
-      <c r="B305" s="6"/>
-    </row>
-    <row r="306" spans="1:2">
+      <c r="B305" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="J305" s="21"/>
+    </row>
+    <row r="306" spans="1:10">
       <c r="A306" s="5">
         <v>305</v>
       </c>
-      <c r="B306" s="6"/>
-    </row>
-    <row r="307" spans="1:2">
+      <c r="B306" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="307" spans="1:10">
       <c r="A307" s="5">
         <v>306</v>
       </c>
-      <c r="B307" s="6"/>
-    </row>
-    <row r="308" spans="1:2">
+      <c r="B307" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="308" spans="1:10">
       <c r="A308" s="5">
         <v>307</v>
       </c>
-      <c r="B308" s="6"/>
-    </row>
-    <row r="309" spans="1:2">
+      <c r="B308" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="309" spans="1:10">
       <c r="A309" s="5">
         <v>308</v>
       </c>
-      <c r="B309" s="6"/>
-    </row>
-    <row r="310" spans="1:2">
+      <c r="B309" s="6" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="310" spans="1:10">
       <c r="A310" s="5">
         <v>309</v>
       </c>
-      <c r="B310" s="6"/>
-    </row>
-    <row r="311" spans="1:2">
+      <c r="B310" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="311" spans="1:10">
       <c r="A311" s="5">
         <v>310</v>
       </c>
-      <c r="B311" s="6"/>
-    </row>
-    <row r="312" spans="1:2">
+      <c r="B311" s="6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="312" spans="1:10">
       <c r="A312" s="5">
         <v>311</v>
       </c>
-      <c r="B312" s="6"/>
-    </row>
-    <row r="313" spans="1:2">
+      <c r="B312" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E312" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="313" spans="1:10">
       <c r="A313" s="5">
         <v>312</v>
       </c>
-      <c r="B313" s="6"/>
-    </row>
-    <row r="314" spans="1:2">
+      <c r="B313" s="6" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="314" spans="1:10">
       <c r="A314" s="5">
         <v>313</v>
       </c>
-      <c r="B314" s="6"/>
-    </row>
-    <row r="315" spans="1:2">
+      <c r="B314" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="315" spans="1:10">
       <c r="A315" s="5">
         <v>314</v>
       </c>
-      <c r="B315" s="6"/>
-    </row>
-    <row r="316" spans="1:2">
+      <c r="B315" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="316" spans="1:10">
       <c r="A316" s="5">
         <v>315</v>
       </c>
-      <c r="B316" s="6"/>
-    </row>
-    <row r="317" spans="1:2">
+      <c r="B316" s="6" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="317" spans="1:10">
       <c r="A317" s="5">
         <v>316</v>
       </c>
       <c r="B317" s="6"/>
     </row>
-    <row r="318" spans="1:2">
+    <row r="318" spans="1:10">
       <c r="A318" s="5">
         <v>317</v>
       </c>
       <c r="B318" s="6"/>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" spans="1:10">
       <c r="A319" s="5">
         <v>318</v>
       </c>
       <c r="B319" s="6"/>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" spans="1:10">
       <c r="A320" s="5">
         <v>319</v>
       </c>
@@ -4005,25 +4407,25 @@
         <v>340</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D341" s="9" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E341" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F341" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G341" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H341" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="342" spans="1:9">
@@ -4031,19 +4433,19 @@
         <v>341</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E342" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F342" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G342" s="16">
         <v>2</v>
       </c>
       <c r="H342" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="343" spans="1:9">
@@ -4052,16 +4454,16 @@
       </c>
       <c r="B343" s="6"/>
       <c r="E343" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F343" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G343" s="16" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H343" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="344" spans="1:9">
@@ -4069,19 +4471,19 @@
         <v>343</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E344" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F344" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G344" s="16" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H344" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="345" spans="1:9">
@@ -4089,19 +4491,19 @@
         <v>344</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E345" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F345" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G345" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H345" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="346" spans="1:9">
@@ -4109,19 +4511,19 @@
         <v>345</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E346" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F346" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G346" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H346" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="347" spans="1:9">
@@ -4129,19 +4531,19 @@
         <v>346</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E347" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F347" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G347" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H347" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="348" spans="1:9">
@@ -4149,19 +4551,19 @@
         <v>347</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E348" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F348" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G348" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H348" t="s">
         <v>151</v>
-      </c>
-      <c r="H348" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="349" spans="1:9">
@@ -4169,19 +4571,19 @@
         <v>348</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E349" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F349" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G349" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H349" t="s">
         <v>151</v>
-      </c>
-      <c r="H349" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="350" spans="1:9">
@@ -4189,19 +4591,19 @@
         <v>349</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E350" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F350" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G350" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H350" t="s">
         <v>151</v>
-      </c>
-      <c r="H350" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="351" spans="1:9">
@@ -4209,19 +4611,19 @@
         <v>350</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E351" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F351" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G351" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H351" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="352" spans="1:9">
@@ -4230,19 +4632,19 @@
       </c>
       <c r="B352" s="6"/>
       <c r="E352" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F352" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G352" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H352" t="s">
+        <v>153</v>
+      </c>
+      <c r="I352" t="s">
         <v>154</v>
-      </c>
-      <c r="H352" t="s">
-        <v>157</v>
-      </c>
-      <c r="I352" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="353" spans="1:9">
@@ -4250,22 +4652,22 @@
         <v>352</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E353" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F353" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G353" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H353" t="s">
+        <v>153</v>
+      </c>
+      <c r="I353" t="s">
         <v>154</v>
-      </c>
-      <c r="H353" t="s">
-        <v>157</v>
-      </c>
-      <c r="I353" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="354" spans="1:9">
@@ -4316,10 +4718,10 @@
       </c>
       <c r="B361" s="6"/>
       <c r="C361" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E361" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="362" spans="1:9">
@@ -4328,7 +4730,7 @@
       </c>
       <c r="B362" s="6"/>
       <c r="E362" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="363" spans="1:9">
@@ -4337,7 +4739,7 @@
       </c>
       <c r="B363" s="6"/>
       <c r="E363" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="364" spans="1:9">
@@ -4346,7 +4748,7 @@
       </c>
       <c r="B364" s="6"/>
       <c r="E364" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="365" spans="1:9">
@@ -4355,7 +4757,7 @@
       </c>
       <c r="B365" s="6"/>
       <c r="E365" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="366" spans="1:9">
@@ -4364,7 +4766,7 @@
       </c>
       <c r="B366" s="6"/>
       <c r="E366" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="367" spans="1:9">
@@ -4373,7 +4775,7 @@
       </c>
       <c r="B367" s="6"/>
       <c r="E367" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="368" spans="1:9">
@@ -4382,7 +4784,7 @@
       </c>
       <c r="B368" s="6"/>
       <c r="E368" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -4403,13 +4805,13 @@
       </c>
       <c r="B371" s="6"/>
       <c r="C371" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E371" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F371" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="372" spans="1:8">
@@ -4418,10 +4820,10 @@
       </c>
       <c r="B372" s="6"/>
       <c r="E372" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F372" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="373" spans="1:8">
@@ -4429,10 +4831,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E373" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="374" spans="1:8">
@@ -4440,64 +4842,85 @@
         <v>373</v>
       </c>
       <c r="B374" s="6"/>
+      <c r="E374" t="s">
+        <v>377</v>
+      </c>
     </row>
     <row r="375" spans="1:8">
       <c r="A375" s="5">
         <v>374</v>
       </c>
       <c r="B375" s="6"/>
+      <c r="E375" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="376" spans="1:8">
       <c r="A376" s="5">
         <v>375</v>
       </c>
       <c r="B376" s="6"/>
+      <c r="E376" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="377" spans="1:8">
       <c r="A377" s="5">
         <v>376</v>
       </c>
       <c r="B377" s="6"/>
+      <c r="E377" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="378" spans="1:8">
       <c r="A378" s="5">
         <v>377</v>
       </c>
       <c r="B378" s="6"/>
+      <c r="E378" t="s">
+        <v>379</v>
+      </c>
     </row>
     <row r="379" spans="1:8">
       <c r="A379" s="5">
         <v>378</v>
       </c>
       <c r="B379" s="6"/>
+      <c r="E379" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="380" spans="1:8">
       <c r="A380" s="5">
         <v>379</v>
       </c>
       <c r="B380" s="6"/>
+      <c r="E380" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="381" spans="1:8">
       <c r="A381" s="5">
         <v>380</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E381" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F381" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G381" s="16" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H381" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -4505,19 +4928,19 @@
         <v>381</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E382" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F382" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G382" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H382" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -4525,19 +4948,19 @@
         <v>382</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E383" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F383" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G383" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H383" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -4545,19 +4968,19 @@
         <v>383</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E384" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F384" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G384" s="16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H384" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="385" spans="1:10">
@@ -4565,19 +4988,19 @@
         <v>384</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E385" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F385" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G385" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H385" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="386" spans="1:10">
@@ -4585,19 +5008,19 @@
         <v>385</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E386" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F386" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G386" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H386" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="387" spans="1:10">
@@ -4605,19 +5028,19 @@
         <v>386</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E387" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F387" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G387" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H387" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="388" spans="1:10">
@@ -4625,19 +5048,19 @@
         <v>387</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E388" t="s">
+        <v>166</v>
+      </c>
+      <c r="F388" t="s">
         <v>170</v>
       </c>
-      <c r="F388" t="s">
-        <v>174</v>
-      </c>
       <c r="G388" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H388" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="389" spans="1:10">
@@ -4645,19 +5068,19 @@
         <v>388</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E389" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F389" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G389" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H389" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="390" spans="1:10">
@@ -4665,19 +5088,19 @@
         <v>389</v>
       </c>
       <c r="B390" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E390" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F390" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G390" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H390" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="391" spans="1:10">
@@ -4685,25 +5108,25 @@
         <v>390</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E391" t="s">
+        <v>178</v>
+      </c>
+      <c r="F391" t="s">
+        <v>144</v>
+      </c>
+      <c r="G391" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="H391" t="s">
+        <v>145</v>
+      </c>
+      <c r="I391" t="s">
+        <v>180</v>
+      </c>
+      <c r="J391" s="16" t="s">
         <v>182</v>
-      </c>
-      <c r="F391" t="s">
-        <v>148</v>
-      </c>
-      <c r="G391" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="H391" t="s">
-        <v>149</v>
-      </c>
-      <c r="I391" t="s">
-        <v>184</v>
-      </c>
-      <c r="J391" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="392" spans="1:10">
@@ -4712,16 +5135,16 @@
       </c>
       <c r="B392" s="6"/>
       <c r="E392" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F392" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G392" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H392" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="393" spans="1:10">
@@ -4729,19 +5152,19 @@
         <v>392</v>
       </c>
       <c r="B393" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E393" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F393" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G393" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H393" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="394" spans="1:10">
@@ -4749,19 +5172,19 @@
         <v>393</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E394" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F394" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G394" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H394" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="395" spans="1:10">
@@ -4769,19 +5192,19 @@
         <v>394</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E395" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F395" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G395" s="16" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H395" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="396" spans="1:10">
@@ -4789,19 +5212,19 @@
         <v>395</v>
       </c>
       <c r="B396" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E396" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F396" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G396" s="16" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H396" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="397" spans="1:10">
@@ -4809,19 +5232,19 @@
         <v>396</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E397" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F397" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G397" s="16" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H397" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="398" spans="1:10">
@@ -4829,19 +5252,19 @@
         <v>397</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E398" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F398" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G398" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H398" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="399" spans="1:10">
@@ -4849,19 +5272,19 @@
         <v>398</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E399" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F399" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G399" s="16" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H399" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="400" spans="1:10">
@@ -4869,19 +5292,19 @@
         <v>399</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E400" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F400" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G400" s="16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H400" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="401" spans="1:9">
@@ -4889,22 +5312,22 @@
         <v>400</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E401" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F401" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G401" s="16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H401" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I401" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="402" spans="1:9">
@@ -4912,22 +5335,22 @@
         <v>401</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E402" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F402" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G402" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H402" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I402" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="403" spans="1:9">
@@ -4983,22 +5406,22 @@
         <v>410</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E411" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F411" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G411" s="16" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H411" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="412" spans="1:9">
@@ -5006,19 +5429,19 @@
         <v>411</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E412" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F412" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G412" s="16" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H412" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="413" spans="1:9">
@@ -5026,19 +5449,19 @@
         <v>412</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E413" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F413" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G413" s="16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H413" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="414" spans="1:9">
@@ -5046,19 +5469,19 @@
         <v>413</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E414" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F414" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G414" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H414" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="415" spans="1:9">
@@ -5066,19 +5489,19 @@
         <v>414</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E415" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F415" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G415" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H415" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="416" spans="1:9">
@@ -5086,19 +5509,19 @@
         <v>415</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E416" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F416" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G416" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H416" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="417" spans="1:9">
@@ -5107,16 +5530,16 @@
       </c>
       <c r="B417" s="6"/>
       <c r="E417" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F417" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G417" s="16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H417" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="418" spans="1:9">
@@ -5125,16 +5548,16 @@
       </c>
       <c r="B418" s="6"/>
       <c r="E418" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F418" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G418" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H418" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="419" spans="1:9">
@@ -5142,19 +5565,19 @@
         <v>418</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E419" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F419" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G419" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H419" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="420" spans="1:9">
@@ -5162,19 +5585,19 @@
         <v>419</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E420" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F420" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="G420" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H420" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="421" spans="1:9">
@@ -5182,19 +5605,19 @@
         <v>420</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E421" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F421" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G421" s="16" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H421" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="422" spans="1:9">
@@ -5202,19 +5625,19 @@
         <v>421</v>
       </c>
       <c r="B422" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E422" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F422" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G422" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H422" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="423" spans="1:9">
@@ -5222,19 +5645,19 @@
         <v>422</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E423" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F423" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G423" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H423" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="424" spans="1:9">
@@ -5242,19 +5665,19 @@
         <v>423</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E424" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F424" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G424" s="16" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H424" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="425" spans="1:9">
@@ -5262,22 +5685,22 @@
         <v>424</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E425" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F425" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G425" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H425" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I425" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="426" spans="1:9">
@@ -5285,22 +5708,22 @@
         <v>425</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E426" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F426" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="G426" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H426" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="I426" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="427" spans="1:9">
@@ -5308,22 +5731,22 @@
         <v>426</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E427" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F427" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G427" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H427" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I427" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="428" spans="1:9">
@@ -5350,7 +5773,7 @@
       </c>
       <c r="B431" s="6"/>
       <c r="C431" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="432" spans="1:9">
@@ -5472,19 +5895,19 @@
         <v>450</v>
       </c>
       <c r="B451" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E451" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G451" s="16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H451" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="452" spans="1:9">
@@ -5492,16 +5915,16 @@
         <v>451</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E452" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G452" s="16" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H452" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="453" spans="1:9">
@@ -5509,16 +5932,16 @@
         <v>452</v>
       </c>
       <c r="B453" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E453" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G453" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H453" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="454" spans="1:9">
@@ -5526,16 +5949,16 @@
         <v>453</v>
       </c>
       <c r="B454" s="6" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E454" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G454" s="16" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H454" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="455" spans="1:9">
@@ -5543,16 +5966,16 @@
         <v>454</v>
       </c>
       <c r="B455" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E455" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G455" s="16" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H455" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="456" spans="1:9">
@@ -5560,16 +5983,16 @@
         <v>455</v>
       </c>
       <c r="B456" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E456" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G456" s="16" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H456" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="457" spans="1:9">
@@ -5577,13 +6000,13 @@
         <v>456</v>
       </c>
       <c r="B457" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E457" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G457" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="458" spans="1:9">
@@ -5591,16 +6014,16 @@
         <v>457</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E458" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G458" s="16" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="H458" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="459" spans="1:9">
@@ -5608,16 +6031,16 @@
         <v>458</v>
       </c>
       <c r="B459" s="6" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E459" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G459" s="16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H459" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="460" spans="1:9">
@@ -5626,7 +6049,7 @@
       </c>
       <c r="B460" s="6"/>
       <c r="E460" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="461" spans="1:9">
@@ -5635,7 +6058,7 @@
       </c>
       <c r="B461" s="6"/>
       <c r="E461" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="462" spans="1:9">
@@ -5644,7 +6067,7 @@
       </c>
       <c r="B462" s="6"/>
       <c r="E462" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="463" spans="1:9">
@@ -5653,7 +6076,7 @@
       </c>
       <c r="B463" s="6"/>
       <c r="I463" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="464" spans="1:9">
@@ -5662,7 +6085,7 @@
       </c>
       <c r="B464" s="6"/>
       <c r="I464" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="465" spans="1:9">
@@ -5671,7 +6094,7 @@
       </c>
       <c r="B465" s="6"/>
       <c r="I465" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="466" spans="1:9">
@@ -5680,7 +6103,7 @@
       </c>
       <c r="B466" s="6"/>
       <c r="I466" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="467" spans="1:9">
@@ -5689,7 +6112,7 @@
       </c>
       <c r="B467" s="6"/>
       <c r="I467" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="468" spans="1:9">
@@ -5698,7 +6121,7 @@
       </c>
       <c r="B468" s="6"/>
       <c r="I468" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="469" spans="1:9">
@@ -5773,100 +6196,148 @@
       </c>
       <c r="B480" s="6"/>
     </row>
-    <row r="481" spans="1:3">
+    <row r="481" spans="1:8">
       <c r="A481" s="5">
         <v>480</v>
       </c>
-      <c r="B481" s="6"/>
+      <c r="B481" s="6" t="s">
+        <v>384</v>
+      </c>
       <c r="C481" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3">
+        <v>282</v>
+      </c>
+      <c r="H481" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8">
       <c r="A482" s="5">
         <v>481</v>
       </c>
-      <c r="B482" s="6"/>
-    </row>
-    <row r="483" spans="1:3">
+      <c r="B482" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="H482" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8">
       <c r="A483" s="5">
         <v>482</v>
       </c>
-      <c r="B483" s="6"/>
-    </row>
-    <row r="484" spans="1:3">
+      <c r="B483" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="H483" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8">
       <c r="A484" s="5">
         <v>483</v>
       </c>
-      <c r="B484" s="6"/>
-    </row>
-    <row r="485" spans="1:3">
+      <c r="B484" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="H484" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8">
       <c r="A485" s="5">
         <v>484</v>
       </c>
-      <c r="B485" s="6"/>
-    </row>
-    <row r="486" spans="1:3">
+      <c r="B485" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="H485" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8">
       <c r="A486" s="5">
         <v>485</v>
       </c>
       <c r="B486" s="6"/>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:8">
       <c r="A487" s="5">
         <v>486</v>
       </c>
       <c r="B487" s="6"/>
-    </row>
-    <row r="488" spans="1:3">
+      <c r="E487" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8">
       <c r="A488" s="5">
         <v>487</v>
       </c>
       <c r="B488" s="6"/>
-    </row>
-    <row r="489" spans="1:3">
+      <c r="E488" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8">
       <c r="A489" s="5">
         <v>488</v>
       </c>
       <c r="B489" s="6"/>
-    </row>
-    <row r="490" spans="1:3">
+      <c r="E489" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8">
       <c r="A490" s="5">
         <v>489</v>
       </c>
       <c r="B490" s="6"/>
-    </row>
-    <row r="491" spans="1:3">
+      <c r="E490" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8">
       <c r="A491" s="5">
         <v>490</v>
       </c>
       <c r="B491" s="6"/>
-    </row>
-    <row r="492" spans="1:3">
+      <c r="E491" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8">
       <c r="A492" s="5">
         <v>491</v>
       </c>
-      <c r="B492" s="6"/>
-    </row>
-    <row r="493" spans="1:3">
+      <c r="B492" s="6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8">
       <c r="A493" s="5">
         <v>492</v>
       </c>
-      <c r="B493" s="6"/>
-    </row>
-    <row r="494" spans="1:3">
+      <c r="B493" s="6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8">
       <c r="A494" s="5">
         <v>493</v>
       </c>
-      <c r="B494" s="6"/>
-    </row>
-    <row r="495" spans="1:3">
+      <c r="B494" s="6" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8">
       <c r="A495" s="5">
         <v>494</v>
       </c>
-      <c r="B495" s="6"/>
-    </row>
-    <row r="496" spans="1:3">
+      <c r="B495" s="6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8">
       <c r="A496" s="5">
         <v>495</v>
       </c>
@@ -5900,12 +6371,14 @@
       <c r="A501" s="5">
         <v>500</v>
       </c>
-      <c r="B501" s="6"/>
+      <c r="B501" s="6" t="s">
+        <v>400</v>
+      </c>
       <c r="C501" s="3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D501" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -5968,7 +6441,7 @@
       </c>
       <c r="B511" s="6"/>
       <c r="C511" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="512" spans="1:4">
@@ -6031,7 +6504,7 @@
       </c>
       <c r="B521" s="6"/>
       <c r="C521" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -6094,7 +6567,7 @@
       </c>
       <c r="B531" s="6"/>
       <c r="C531" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -6157,7 +6630,7 @@
       </c>
       <c r="B541" s="6"/>
       <c r="C541" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -6274,289 +6747,310 @@
       </c>
       <c r="B560" s="6"/>
     </row>
-    <row r="561" spans="1:2">
+    <row r="561" spans="1:5">
       <c r="A561" s="5">
         <v>560</v>
       </c>
       <c r="B561" s="6"/>
-    </row>
-    <row r="562" spans="1:2">
+      <c r="C561" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="D561" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E561" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5">
       <c r="A562" s="5">
         <v>561</v>
       </c>
       <c r="B562" s="6"/>
     </row>
-    <row r="563" spans="1:2">
+    <row r="563" spans="1:5">
       <c r="A563" s="5">
         <v>562</v>
       </c>
       <c r="B563" s="6"/>
     </row>
-    <row r="564" spans="1:2">
+    <row r="564" spans="1:5">
       <c r="A564" s="5">
         <v>563</v>
       </c>
       <c r="B564" s="6"/>
     </row>
-    <row r="565" spans="1:2">
+    <row r="565" spans="1:5">
       <c r="A565" s="5">
         <v>564</v>
       </c>
       <c r="B565" s="6"/>
     </row>
-    <row r="566" spans="1:2">
+    <row r="566" spans="1:5">
       <c r="A566" s="5">
         <v>565</v>
       </c>
       <c r="B566" s="6"/>
     </row>
-    <row r="567" spans="1:2">
+    <row r="567" spans="1:5">
       <c r="A567" s="5">
         <v>566</v>
       </c>
       <c r="B567" s="6"/>
     </row>
-    <row r="568" spans="1:2">
+    <row r="568" spans="1:5">
       <c r="A568" s="5">
         <v>567</v>
       </c>
       <c r="B568" s="6"/>
     </row>
-    <row r="569" spans="1:2">
+    <row r="569" spans="1:5">
       <c r="A569" s="5">
         <v>568</v>
       </c>
       <c r="B569" s="6"/>
     </row>
-    <row r="570" spans="1:2">
+    <row r="570" spans="1:5">
       <c r="A570" s="5">
         <v>569</v>
       </c>
       <c r="B570" s="6"/>
     </row>
-    <row r="571" spans="1:2">
+    <row r="571" spans="1:5">
       <c r="A571" s="5">
         <v>570</v>
       </c>
       <c r="B571" s="6"/>
-    </row>
-    <row r="572" spans="1:2">
+      <c r="C571" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5">
       <c r="A572" s="5">
         <v>571</v>
       </c>
       <c r="B572" s="6"/>
     </row>
-    <row r="573" spans="1:2">
+    <row r="573" spans="1:5">
       <c r="A573" s="5">
         <v>572</v>
       </c>
       <c r="B573" s="6"/>
     </row>
-    <row r="574" spans="1:2">
+    <row r="574" spans="1:5">
       <c r="A574" s="5">
         <v>573</v>
       </c>
       <c r="B574" s="6"/>
     </row>
-    <row r="575" spans="1:2">
+    <row r="575" spans="1:5">
       <c r="A575" s="5">
         <v>574</v>
       </c>
       <c r="B575" s="6"/>
     </row>
-    <row r="576" spans="1:2">
+    <row r="576" spans="1:5">
       <c r="A576" s="5">
         <v>575</v>
       </c>
       <c r="B576" s="6"/>
     </row>
-    <row r="577" spans="1:2">
+    <row r="577" spans="1:3">
       <c r="A577" s="5">
         <v>576</v>
       </c>
       <c r="B577" s="6"/>
     </row>
-    <row r="578" spans="1:2">
+    <row r="578" spans="1:3">
       <c r="A578" s="5">
         <v>577</v>
       </c>
       <c r="B578" s="6"/>
     </row>
-    <row r="579" spans="1:2">
+    <row r="579" spans="1:3">
       <c r="A579" s="5">
         <v>578</v>
       </c>
       <c r="B579" s="6"/>
     </row>
-    <row r="580" spans="1:2">
+    <row r="580" spans="1:3">
       <c r="A580" s="5">
         <v>579</v>
       </c>
       <c r="B580" s="6"/>
     </row>
-    <row r="581" spans="1:2">
+    <row r="581" spans="1:3">
       <c r="A581" s="5">
         <v>580</v>
       </c>
       <c r="B581" s="6"/>
-    </row>
-    <row r="582" spans="1:2">
+      <c r="C581" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3">
       <c r="A582" s="5">
         <v>581</v>
       </c>
       <c r="B582" s="6"/>
     </row>
-    <row r="583" spans="1:2">
+    <row r="583" spans="1:3">
       <c r="A583" s="5">
         <v>582</v>
       </c>
       <c r="B583" s="6"/>
     </row>
-    <row r="584" spans="1:2">
+    <row r="584" spans="1:3">
       <c r="A584" s="5">
         <v>583</v>
       </c>
       <c r="B584" s="6"/>
     </row>
-    <row r="585" spans="1:2">
+    <row r="585" spans="1:3">
       <c r="A585" s="5">
         <v>584</v>
       </c>
       <c r="B585" s="6"/>
     </row>
-    <row r="586" spans="1:2">
+    <row r="586" spans="1:3">
       <c r="A586" s="5">
         <v>585</v>
       </c>
       <c r="B586" s="6"/>
     </row>
-    <row r="587" spans="1:2">
+    <row r="587" spans="1:3">
       <c r="A587" s="5">
         <v>586</v>
       </c>
       <c r="B587" s="6"/>
     </row>
-    <row r="588" spans="1:2">
+    <row r="588" spans="1:3">
       <c r="A588" s="5">
         <v>587</v>
       </c>
       <c r="B588" s="6"/>
     </row>
-    <row r="589" spans="1:2">
+    <row r="589" spans="1:3">
       <c r="A589" s="5">
         <v>588</v>
       </c>
       <c r="B589" s="6"/>
     </row>
-    <row r="590" spans="1:2">
+    <row r="590" spans="1:3">
       <c r="A590" s="5">
         <v>589</v>
       </c>
       <c r="B590" s="6"/>
     </row>
-    <row r="591" spans="1:2">
+    <row r="591" spans="1:3">
       <c r="A591" s="5">
         <v>590</v>
       </c>
       <c r="B591" s="6"/>
-    </row>
-    <row r="592" spans="1:2">
+      <c r="C591" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3">
       <c r="A592" s="5">
         <v>591</v>
       </c>
       <c r="B592" s="6"/>
     </row>
-    <row r="593" spans="1:2">
+    <row r="593" spans="1:3">
       <c r="A593" s="5">
         <v>592</v>
       </c>
       <c r="B593" s="6"/>
     </row>
-    <row r="594" spans="1:2">
+    <row r="594" spans="1:3">
       <c r="A594" s="5">
         <v>593</v>
       </c>
       <c r="B594" s="6"/>
     </row>
-    <row r="595" spans="1:2">
+    <row r="595" spans="1:3">
       <c r="A595" s="5">
         <v>594</v>
       </c>
       <c r="B595" s="6"/>
     </row>
-    <row r="596" spans="1:2">
+    <row r="596" spans="1:3">
       <c r="A596" s="5">
         <v>595</v>
       </c>
       <c r="B596" s="6"/>
     </row>
-    <row r="597" spans="1:2">
+    <row r="597" spans="1:3">
       <c r="A597" s="5">
         <v>596</v>
       </c>
       <c r="B597" s="6"/>
     </row>
-    <row r="598" spans="1:2">
+    <row r="598" spans="1:3">
       <c r="A598" s="5">
         <v>597</v>
       </c>
       <c r="B598" s="6"/>
     </row>
-    <row r="599" spans="1:2">
+    <row r="599" spans="1:3">
       <c r="A599" s="5">
         <v>598</v>
       </c>
       <c r="B599" s="6"/>
     </row>
-    <row r="600" spans="1:2">
+    <row r="600" spans="1:3">
       <c r="A600" s="5">
         <v>599</v>
       </c>
       <c r="B600" s="6"/>
     </row>
-    <row r="601" spans="1:2">
+    <row r="601" spans="1:3">
       <c r="A601" s="5">
         <v>600</v>
       </c>
       <c r="B601" s="6"/>
-    </row>
-    <row r="602" spans="1:2">
+      <c r="C601" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3">
       <c r="A602" s="5">
         <v>601</v>
       </c>
       <c r="B602" s="6"/>
     </row>
-    <row r="603" spans="1:2">
+    <row r="603" spans="1:3">
       <c r="A603" s="5">
         <v>602</v>
       </c>
       <c r="B603" s="6"/>
     </row>
-    <row r="604" spans="1:2">
+    <row r="604" spans="1:3">
       <c r="A604" s="5">
         <v>603</v>
       </c>
       <c r="B604" s="6"/>
     </row>
-    <row r="605" spans="1:2">
+    <row r="605" spans="1:3">
       <c r="A605" s="5">
         <v>604</v>
       </c>
       <c r="B605" s="6"/>
     </row>
-    <row r="606" spans="1:2">
+    <row r="606" spans="1:3">
       <c r="A606" s="5">
         <v>605</v>
       </c>
       <c r="B606" s="6"/>
     </row>
-    <row r="607" spans="1:2">
+    <row r="607" spans="1:3">
       <c r="A607" s="5">
         <v>606</v>
       </c>
       <c r="B607" s="6"/>
     </row>
-    <row r="608" spans="1:2">
+    <row r="608" spans="1:3">
       <c r="A608" s="5">
         <v>607</v>
       </c>
@@ -8916,10 +9410,19 @@
     </row>
     <row r="1001" spans="1:4">
       <c r="D1001" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="L2:L7"/>
+    <mergeCell ref="J302:J305"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="J31:J34"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J61:J62"/>
+    <mergeCell ref="J86:J87"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
